--- a/inst/cprd/lsoa_prac.xlsx
+++ b/inst/cprd/lsoa_prac.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="practice_imd" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="182">
   <si>
     <t xml:space="preserve">Column name</t>
   </si>
@@ -58,61 +58,64 @@
     <t xml:space="preserve">1=England, 2=Northern Ireland, 3=Scotland, 4=Wales</t>
   </si>
   <si>
+    <t xml:space="preserve">TEXT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e_imd_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">England: IMD2019: quintile (1=LEAST deprived)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e_imd_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">England: IMD2019: decile (1=LEAST deprived)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ni_imd_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern Ireland: MDM2017: quintile (1=LEAST deprived)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ni_imd_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern Ireland: MDM2017: decile (1=LEAST deprived)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s_imd_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scotland: IMD2020: quintile (1=LEAST deprived)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s_imd_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scotland: IMD2020: decile (1=LEAST deprived)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w_imd_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wales: IMD2019: quintile (1=LEAST deprived)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w_imd_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wales: IMD2019: decile (1=LEAST deprived)</t>
+  </si>
+  <si>
     <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e2019_imd_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">England: IMD2019: quintile (1=LEAST deprived)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e2019_imd_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">England: IMD2019: decile (1=LEAST deprived)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ni2017_imd_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern Ireland: MDM2017: quintile (1=LEAST deprived)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ni2017_imd_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern Ireland: MDM2017: decile (1=LEAST deprived)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s2020_imd_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scotland: IMD2020: quintile (1=LEAST deprived)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s2020_imd_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scotland: IMD2020: decile (1=LEAST deprived)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w2019_imd_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wales: IMD2019: quintile (1=LEAST deprived)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w2019_imd_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wales: IMD2019: decile (1=LEAST deprived)</t>
   </si>
   <si>
     <t xml:space="preserve">e2019_income_5</t>
@@ -712,12 +715,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -741,34 +748,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -914,162 +921,165 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="D3" s="1" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="0" t="s">
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="0" t="s">
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="0" t="s">
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="0" t="s">
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1090,960 +1100,960 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D68"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="B5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="B6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="B8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="B9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="B11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="B12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="B13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="B14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="B15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="B16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="B17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="B18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="B19" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="B20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="B21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="B22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="B23" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="B24" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="B25" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="B26" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="B27" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="B28" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="B29" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="B30" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C31" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="B31" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C32" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="B32" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C33" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="B33" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="B34" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="B35" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="B36" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="B37" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="B38" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C39" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="B39" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C40" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="B40" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="B41" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C42" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="B42" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="C42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C43" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="B43" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="C43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C44" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D44" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="B44" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="B45" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C46" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="B46" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C47" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="B47" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C48" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D48" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="B48" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C49" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="B49" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C50" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="B50" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C51" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="B51" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D52" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="B52" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C53" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D53" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="B53" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C54" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="B54" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C55" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="B55" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C56" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D56" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="B56" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C57" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="B57" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C58" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D58" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="B58" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C59" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D59" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="B59" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C60" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="B60" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C61" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D61" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="B61" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C62" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D62" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="B62" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C63" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D63" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="B63" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="C63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C64" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D64" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="B64" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C65" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D65" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="B65" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C66" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D66" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="B66" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C67" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D67" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="B67" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C68" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D68" s="0" t="s">
+      <c r="B68" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2064,61 +2074,64 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.49"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="B2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="B3" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="B4" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2139,64 +2152,64 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="B2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="B3" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="B4" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2217,92 +2230,92 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="B2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="B3" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="B4" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="B5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="B5" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="0" t="s">
+      <c r="B6" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2323,51 +2336,51 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="B2" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>179</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>10</v>
+      <c r="B3" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
